--- a/backend/src/data/patients.xlsx
+++ b/backend/src/data/patients.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>OP Number</t>
   </si>
@@ -74,6 +74,36 @@
   </si>
   <si>
     <t>31/5/2026, 3:33:46 pm</t>
+  </si>
+  <si>
+    <t>OP-2026-5975</t>
+  </si>
+  <si>
+    <t>Praneeth</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>8977410860</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>1-110 Hyderabad</t>
+  </si>
+  <si>
+    <t>Orthopedics</t>
+  </si>
+  <si>
+    <t>Ashok</t>
+  </si>
+  <si>
+    <t>3/6/2026, 4:21:34 pm</t>
   </si>
 </sst>
 </file>
@@ -450,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -556,6 +586,41 @@
       </c>
       <c r="K3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4">
+        <v>500</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/backend/src/data/patients.xlsx
+++ b/backend/src/data/patients.xlsx
@@ -11,12 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="548">
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>OP Number</t>
   </si>
   <si>
-    <t>Full Name</t>
+    <t>Name</t>
   </si>
   <si>
     <t>Age</t>
@@ -31,79 +34,1627 @@
     <t>Blood Group</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
-    <t>Doctor</t>
-  </si>
-  <si>
-    <t>Fee</t>
+    <t>Assigned Doctor</t>
   </si>
   <si>
     <t>Created At</t>
   </si>
   <si>
-    <t>OP-2026-1001</t>
-  </si>
-  <si>
-    <t>Keerthika</t>
+    <t>PAT-A0B06C8B</t>
+  </si>
+  <si>
+    <t>OP001000</t>
+  </si>
+  <si>
+    <t>Rahul Nair</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>9902730466</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>General Medicine</t>
+  </si>
+  <si>
+    <t>Dr. Patel</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:28:42.590Z</t>
+  </si>
+  <si>
+    <t>PAT-8F6D5E18</t>
+  </si>
+  <si>
+    <t>OP001001</t>
+  </si>
+  <si>
+    <t>Arjun Chowdary</t>
   </si>
   <si>
     <t>Female</t>
   </si>
   <si>
-    <t>9876543210</t>
+    <t>9891446999</t>
+  </si>
+  <si>
+    <t>Dr. Reddy</t>
+  </si>
+  <si>
+    <t>PAT-A86C5C37</t>
+  </si>
+  <si>
+    <t>OP001002</t>
+  </si>
+  <si>
+    <t>Ananya Menon</t>
+  </si>
+  <si>
+    <t>9611808645</t>
+  </si>
+  <si>
+    <t>AB-</t>
+  </si>
+  <si>
+    <t>Physiotherapy</t>
+  </si>
+  <si>
+    <t>PAT-A93ED4E0</t>
+  </si>
+  <si>
+    <t>OP001003</t>
+  </si>
+  <si>
+    <t>Sunita Rao</t>
+  </si>
+  <si>
+    <t>9289732990</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Dr. Sharma</t>
+  </si>
+  <si>
+    <t>PAT-13B27116</t>
+  </si>
+  <si>
+    <t>OP001004</t>
+  </si>
+  <si>
+    <t>Vihaan Reddy</t>
+  </si>
+  <si>
+    <t>9416450467</t>
+  </si>
+  <si>
+    <t>Orthopaedics</t>
+  </si>
+  <si>
+    <t>PAT-484C48C4</t>
+  </si>
+  <si>
+    <t>OP001005</t>
+  </si>
+  <si>
+    <t>Ishita Reddy</t>
+  </si>
+  <si>
+    <t>9194378480</t>
+  </si>
+  <si>
+    <t>PAT-13C4476C</t>
+  </si>
+  <si>
+    <t>OP001006</t>
+  </si>
+  <si>
+    <t>9239255049</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>PAT-DE82E56C</t>
+  </si>
+  <si>
+    <t>OP001007</t>
+  </si>
+  <si>
+    <t>Krishna Sharma</t>
+  </si>
+  <si>
+    <t>9875557124</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>PAT-5ECBAE08</t>
+  </si>
+  <si>
+    <t>OP001008</t>
+  </si>
+  <si>
+    <t>Krishna Singh</t>
+  </si>
+  <si>
+    <t>9901238978</t>
+  </si>
+  <si>
+    <t>PAT-35485F8F</t>
+  </si>
+  <si>
+    <t>OP001009</t>
+  </si>
+  <si>
+    <t>Neha Nair</t>
+  </si>
+  <si>
+    <t>9909561601</t>
+  </si>
+  <si>
+    <t>PAT-8AB3F365</t>
+  </si>
+  <si>
+    <t>OP001010</t>
+  </si>
+  <si>
+    <t>Rohan Iyer</t>
+  </si>
+  <si>
+    <t>9925248476</t>
+  </si>
+  <si>
+    <t>PAT-DD356E59</t>
+  </si>
+  <si>
+    <t>OP001011</t>
+  </si>
+  <si>
+    <t>Vikram Reddy</t>
+  </si>
+  <si>
+    <t>9285152776</t>
+  </si>
+  <si>
+    <t>PAT-0E400A4B</t>
+  </si>
+  <si>
+    <t>OP001012</t>
+  </si>
+  <si>
+    <t>Ishita Rao</t>
+  </si>
+  <si>
+    <t>9194599660</t>
+  </si>
+  <si>
+    <t>PAT-EB04E49E</t>
+  </si>
+  <si>
+    <t>OP001013</t>
+  </si>
+  <si>
+    <t>Vikram Singh</t>
+  </si>
+  <si>
+    <t>9271234544</t>
+  </si>
+  <si>
+    <t>PAT-465A4CC0</t>
+  </si>
+  <si>
+    <t>OP001014</t>
+  </si>
+  <si>
+    <t>Krishna Patel</t>
+  </si>
+  <si>
+    <t>9275321060</t>
+  </si>
+  <si>
+    <t>PAT-1DE14465</t>
+  </si>
+  <si>
+    <t>OP001015</t>
+  </si>
+  <si>
+    <t>Arjun Sharma</t>
+  </si>
+  <si>
+    <t>9684139677</t>
+  </si>
+  <si>
+    <t>PAT-9F3D187E</t>
+  </si>
+  <si>
+    <t>OP001016</t>
+  </si>
+  <si>
+    <t>Karan Patel</t>
+  </si>
+  <si>
+    <t>9817127716</t>
   </si>
   <si>
     <t>B+</t>
   </si>
   <si>
-    <t>Hyderabad</t>
-  </si>
-  <si>
-    <t>Orthopaedics</t>
-  </si>
-  <si>
-    <t>Dr Kumar</t>
-  </si>
-  <si>
-    <t>31/5/2026, 3:19:51 pm</t>
-  </si>
-  <si>
-    <t>31/5/2026, 3:33:46 pm</t>
-  </si>
-  <si>
-    <t>OP-2026-5975</t>
-  </si>
-  <si>
-    <t>Praneeth</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>8977410860</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>1-110 Hyderabad</t>
-  </si>
-  <si>
-    <t>Orthopedics</t>
-  </si>
-  <si>
-    <t>Ashok</t>
-  </si>
-  <si>
-    <t>3/6/2026, 4:21:34 pm</t>
+    <t>PAT-66ED3959</t>
+  </si>
+  <si>
+    <t>OP001017</t>
+  </si>
+  <si>
+    <t>Sneha Patel</t>
+  </si>
+  <si>
+    <t>9750453411</t>
+  </si>
+  <si>
+    <t>PAT-0F4F5689</t>
+  </si>
+  <si>
+    <t>OP001018</t>
+  </si>
+  <si>
+    <t>Ravi Patel</t>
+  </si>
+  <si>
+    <t>9922078480</t>
+  </si>
+  <si>
+    <t>PAT-B3A40BD2</t>
+  </si>
+  <si>
+    <t>OP001019</t>
+  </si>
+  <si>
+    <t>Priya Kumar</t>
+  </si>
+  <si>
+    <t>9751128744</t>
+  </si>
+  <si>
+    <t>O-</t>
+  </si>
+  <si>
+    <t>PAT-34B8AAC9</t>
+  </si>
+  <si>
+    <t>OP001020</t>
+  </si>
+  <si>
+    <t>9886018955</t>
+  </si>
+  <si>
+    <t>PAT-98CFBFAC</t>
+  </si>
+  <si>
+    <t>OP001021</t>
+  </si>
+  <si>
+    <t>Krishna Naidu</t>
+  </si>
+  <si>
+    <t>9133091636</t>
+  </si>
+  <si>
+    <t>PAT-7964DCB0</t>
+  </si>
+  <si>
+    <t>OP001022</t>
+  </si>
+  <si>
+    <t>Sneha Reddy</t>
+  </si>
+  <si>
+    <t>9638357287</t>
+  </si>
+  <si>
+    <t>PAT-B141758E</t>
+  </si>
+  <si>
+    <t>OP001023</t>
+  </si>
+  <si>
+    <t>Arjun Kumar</t>
+  </si>
+  <si>
+    <t>9932777056</t>
+  </si>
+  <si>
+    <t>PAT-36ED2284</t>
+  </si>
+  <si>
+    <t>OP001024</t>
+  </si>
+  <si>
+    <t>Krishna Kumar</t>
+  </si>
+  <si>
+    <t>9378909876</t>
+  </si>
+  <si>
+    <t>PAT-B7D5099A</t>
+  </si>
+  <si>
+    <t>OP001025</t>
+  </si>
+  <si>
+    <t>Gita Gowda</t>
+  </si>
+  <si>
+    <t>9394878252</t>
+  </si>
+  <si>
+    <t>PAT-BFA29F5D</t>
+  </si>
+  <si>
+    <t>OP001026</t>
+  </si>
+  <si>
+    <t>Ravi Gowda</t>
+  </si>
+  <si>
+    <t>9044700779</t>
+  </si>
+  <si>
+    <t>PAT-25B64058</t>
+  </si>
+  <si>
+    <t>OP001027</t>
+  </si>
+  <si>
+    <t>Neha Gowda</t>
+  </si>
+  <si>
+    <t>9652602895</t>
+  </si>
+  <si>
+    <t>PAT-17594EA1</t>
+  </si>
+  <si>
+    <t>OP001028</t>
+  </si>
+  <si>
+    <t>Vihaan Patel</t>
+  </si>
+  <si>
+    <t>9652211249</t>
+  </si>
+  <si>
+    <t>PAT-4D979A6B</t>
+  </si>
+  <si>
+    <t>OP001029</t>
+  </si>
+  <si>
+    <t>Sai Kumar</t>
+  </si>
+  <si>
+    <t>9414371295</t>
+  </si>
+  <si>
+    <t>PAT-4AAA3C1D</t>
+  </si>
+  <si>
+    <t>OP001030</t>
+  </si>
+  <si>
+    <t>Sai Iyer</t>
+  </si>
+  <si>
+    <t>9194610363</t>
+  </si>
+  <si>
+    <t>PAT-781A17D8</t>
+  </si>
+  <si>
+    <t>OP001031</t>
+  </si>
+  <si>
+    <t>Vikram Chowdary</t>
+  </si>
+  <si>
+    <t>9995349110</t>
+  </si>
+  <si>
+    <t>PAT-CFF19A49</t>
+  </si>
+  <si>
+    <t>OP001032</t>
+  </si>
+  <si>
+    <t>Saanvi Kumar</t>
+  </si>
+  <si>
+    <t>9910642912</t>
+  </si>
+  <si>
+    <t>PAT-49C949AC</t>
+  </si>
+  <si>
+    <t>OP001033</t>
+  </si>
+  <si>
+    <t>Pooja Reddy</t>
+  </si>
+  <si>
+    <t>9037589740</t>
+  </si>
+  <si>
+    <t>PAT-FF3DAE13</t>
+  </si>
+  <si>
+    <t>OP001034</t>
+  </si>
+  <si>
+    <t>Ravi Sharma</t>
+  </si>
+  <si>
+    <t>9692884520</t>
+  </si>
+  <si>
+    <t>PAT-4D33A850</t>
+  </si>
+  <si>
+    <t>OP001035</t>
+  </si>
+  <si>
+    <t>Rohan Singh</t>
+  </si>
+  <si>
+    <t>9816738302</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-C761C153</t>
+  </si>
+  <si>
+    <t>OP001036</t>
+  </si>
+  <si>
+    <t>Aarav Gowda</t>
+  </si>
+  <si>
+    <t>9560585646</t>
+  </si>
+  <si>
+    <t>PAT-F72FA1CE</t>
+  </si>
+  <si>
+    <t>OP001037</t>
+  </si>
+  <si>
+    <t>Sneha Naidu</t>
+  </si>
+  <si>
+    <t>9388579513</t>
+  </si>
+  <si>
+    <t>PAT-76C4D01B</t>
+  </si>
+  <si>
+    <t>OP001038</t>
+  </si>
+  <si>
+    <t>Gita Sharma</t>
+  </si>
+  <si>
+    <t>9833422535</t>
+  </si>
+  <si>
+    <t>PAT-D1E00955</t>
+  </si>
+  <si>
+    <t>OP001039</t>
+  </si>
+  <si>
+    <t>Saanvi Reddy</t>
+  </si>
+  <si>
+    <t>9674628668</t>
+  </si>
+  <si>
+    <t>PAT-2184465F</t>
+  </si>
+  <si>
+    <t>OP001040</t>
+  </si>
+  <si>
+    <t>Rohan Naidu</t>
+  </si>
+  <si>
+    <t>9959229758</t>
+  </si>
+  <si>
+    <t>2026-05-08T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-DD72FDB4</t>
+  </si>
+  <si>
+    <t>OP001041</t>
+  </si>
+  <si>
+    <t>Vihaan Naidu</t>
+  </si>
+  <si>
+    <t>9690198686</t>
+  </si>
+  <si>
+    <t>2026-05-20T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-5047FBFC</t>
+  </si>
+  <si>
+    <t>OP001042</t>
+  </si>
+  <si>
+    <t>Krishna Reddy</t>
+  </si>
+  <si>
+    <t>9204693673</t>
+  </si>
+  <si>
+    <t>2026-05-13T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-7A11566E</t>
+  </si>
+  <si>
+    <t>OP001043</t>
+  </si>
+  <si>
+    <t>Suresh Kumar</t>
+  </si>
+  <si>
+    <t>9802684230</t>
+  </si>
+  <si>
+    <t>2026-05-25T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-3F93F395</t>
+  </si>
+  <si>
+    <t>OP001044</t>
+  </si>
+  <si>
+    <t>Ananya Kumar</t>
+  </si>
+  <si>
+    <t>9922940060</t>
+  </si>
+  <si>
+    <t>PAT-3BDD997D</t>
+  </si>
+  <si>
+    <t>OP001045</t>
+  </si>
+  <si>
+    <t>Karan Iyer</t>
+  </si>
+  <si>
+    <t>9472195298</t>
+  </si>
+  <si>
+    <t>2026-06-01T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-803D4F4F</t>
+  </si>
+  <si>
+    <t>OP001046</t>
+  </si>
+  <si>
+    <t>Aditya Gowda</t>
+  </si>
+  <si>
+    <t>9199863594</t>
+  </si>
+  <si>
+    <t>2026-05-21T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-33C276EB</t>
+  </si>
+  <si>
+    <t>OP001047</t>
+  </si>
+  <si>
+    <t>Suresh Reddy</t>
+  </si>
+  <si>
+    <t>9683359906</t>
+  </si>
+  <si>
+    <t>2026-06-03T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-3096F817</t>
+  </si>
+  <si>
+    <t>OP001048</t>
+  </si>
+  <si>
+    <t>Ishita Singh</t>
+  </si>
+  <si>
+    <t>9723125807</t>
+  </si>
+  <si>
+    <t>2026-05-17T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-47A17A5B</t>
+  </si>
+  <si>
+    <t>OP001049</t>
+  </si>
+  <si>
+    <t>9640140891</t>
+  </si>
+  <si>
+    <t>PAT-FBECB832</t>
+  </si>
+  <si>
+    <t>OP001050</t>
+  </si>
+  <si>
+    <t>Ravi Nair</t>
+  </si>
+  <si>
+    <t>9129586183</t>
+  </si>
+  <si>
+    <t>PAT-70C54A7D</t>
+  </si>
+  <si>
+    <t>OP001051</t>
+  </si>
+  <si>
+    <t>Priya Reddy</t>
+  </si>
+  <si>
+    <t>9334811650</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>PAT-CCD0EAE1</t>
+  </si>
+  <si>
+    <t>OP001052</t>
+  </si>
+  <si>
+    <t>Ramesh Iyer</t>
+  </si>
+  <si>
+    <t>9544292303</t>
+  </si>
+  <si>
+    <t>PAT-823DC348</t>
+  </si>
+  <si>
+    <t>OP001053</t>
+  </si>
+  <si>
+    <t>Arjun Iyer</t>
+  </si>
+  <si>
+    <t>9394856656</t>
+  </si>
+  <si>
+    <t>2026-05-10T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-9D80B7CE</t>
+  </si>
+  <si>
+    <t>OP001054</t>
+  </si>
+  <si>
+    <t>9292309139</t>
+  </si>
+  <si>
+    <t>2026-05-23T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-88733246</t>
+  </si>
+  <si>
+    <t>OP001055</t>
+  </si>
+  <si>
+    <t>Sunita Singh</t>
+  </si>
+  <si>
+    <t>9995090892</t>
+  </si>
+  <si>
+    <t>2026-05-11T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-5DFA9F77</t>
+  </si>
+  <si>
+    <t>OP001056</t>
+  </si>
+  <si>
+    <t>Krishna Iyer</t>
+  </si>
+  <si>
+    <t>9349950468</t>
+  </si>
+  <si>
+    <t>PAT-0F1616F4</t>
+  </si>
+  <si>
+    <t>OP001057</t>
+  </si>
+  <si>
+    <t>Priya Sharma</t>
+  </si>
+  <si>
+    <t>9866190543</t>
+  </si>
+  <si>
+    <t>PAT-8262E439</t>
+  </si>
+  <si>
+    <t>OP001058</t>
+  </si>
+  <si>
+    <t>Ravi Kumar</t>
+  </si>
+  <si>
+    <t>9220687855</t>
+  </si>
+  <si>
+    <t>2026-05-16T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-84C6B92B</t>
+  </si>
+  <si>
+    <t>OP001059</t>
+  </si>
+  <si>
+    <t>Saanvi Sharma</t>
+  </si>
+  <si>
+    <t>9325216829</t>
+  </si>
+  <si>
+    <t>PAT-A867E17B</t>
+  </si>
+  <si>
+    <t>OP001060</t>
+  </si>
+  <si>
+    <t>Kavya Naidu</t>
+  </si>
+  <si>
+    <t>9934921316</t>
+  </si>
+  <si>
+    <t>2026-05-15T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-F9B33C3F</t>
+  </si>
+  <si>
+    <t>OP001061</t>
+  </si>
+  <si>
+    <t>Suresh Nair</t>
+  </si>
+  <si>
+    <t>9613407350</t>
+  </si>
+  <si>
+    <t>2026-05-24T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-3235C40A</t>
+  </si>
+  <si>
+    <t>OP001062</t>
+  </si>
+  <si>
+    <t>Ramesh Singh</t>
+  </si>
+  <si>
+    <t>9230224690</t>
+  </si>
+  <si>
+    <t>2026-05-26T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-28676C2F</t>
+  </si>
+  <si>
+    <t>OP001063</t>
+  </si>
+  <si>
+    <t>Arjun Gowda</t>
+  </si>
+  <si>
+    <t>9703022752</t>
+  </si>
+  <si>
+    <t>2026-05-18T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-4BBE8752</t>
+  </si>
+  <si>
+    <t>OP001064</t>
+  </si>
+  <si>
+    <t>Ananya Gowda</t>
+  </si>
+  <si>
+    <t>9403548757</t>
+  </si>
+  <si>
+    <t>2026-05-19T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-0F971607</t>
+  </si>
+  <si>
+    <t>OP001065</t>
+  </si>
+  <si>
+    <t>Sunita Sharma</t>
+  </si>
+  <si>
+    <t>9148558757</t>
+  </si>
+  <si>
+    <t>2026-05-14T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-C9E559B9</t>
+  </si>
+  <si>
+    <t>OP001066</t>
+  </si>
+  <si>
+    <t>Vihaan Rao</t>
+  </si>
+  <si>
+    <t>9126697315</t>
+  </si>
+  <si>
+    <t>PAT-D3266763</t>
+  </si>
+  <si>
+    <t>OP001067</t>
+  </si>
+  <si>
+    <t>Gita Chowdary</t>
+  </si>
+  <si>
+    <t>9009597138</t>
+  </si>
+  <si>
+    <t>PAT-22E2B37F</t>
+  </si>
+  <si>
+    <t>OP001068</t>
+  </si>
+  <si>
+    <t>Suresh Naidu</t>
+  </si>
+  <si>
+    <t>9809602670</t>
+  </si>
+  <si>
+    <t>2026-05-09T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-3FE16E6C</t>
+  </si>
+  <si>
+    <t>OP001069</t>
+  </si>
+  <si>
+    <t>Kavya Reddy</t>
+  </si>
+  <si>
+    <t>9020845375</t>
+  </si>
+  <si>
+    <t>PAT-5274D508</t>
+  </si>
+  <si>
+    <t>OP001070</t>
+  </si>
+  <si>
+    <t>Saanvi Naidu</t>
+  </si>
+  <si>
+    <t>9140000945</t>
+  </si>
+  <si>
+    <t>PAT-C3AFBC88</t>
+  </si>
+  <si>
+    <t>OP001071</t>
+  </si>
+  <si>
+    <t>Sai Sharma</t>
+  </si>
+  <si>
+    <t>9153003601</t>
+  </si>
+  <si>
+    <t>PAT-6EA9479A</t>
+  </si>
+  <si>
+    <t>OP001072</t>
+  </si>
+  <si>
+    <t>9530343575</t>
+  </si>
+  <si>
+    <t>2026-05-27T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-2FA40757</t>
+  </si>
+  <si>
+    <t>OP001073</t>
+  </si>
+  <si>
+    <t>Rohan Sharma</t>
+  </si>
+  <si>
+    <t>9664877316</t>
+  </si>
+  <si>
+    <t>2026-05-29T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-3B550FD8</t>
+  </si>
+  <si>
+    <t>OP001074</t>
+  </si>
+  <si>
+    <t>Priya Nair</t>
+  </si>
+  <si>
+    <t>9514792611</t>
+  </si>
+  <si>
+    <t>PAT-28DB391F</t>
+  </si>
+  <si>
+    <t>OP001075</t>
+  </si>
+  <si>
+    <t>Rahul Reddy</t>
+  </si>
+  <si>
+    <t>9498166081</t>
+  </si>
+  <si>
+    <t>2026-05-06T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-6B45DE9E</t>
+  </si>
+  <si>
+    <t>OP001076</t>
+  </si>
+  <si>
+    <t>9459976413</t>
+  </si>
+  <si>
+    <t>PAT-C039E7F8</t>
+  </si>
+  <si>
+    <t>OP001077</t>
+  </si>
+  <si>
+    <t>9411713672</t>
+  </si>
+  <si>
+    <t>PAT-0C7DABC1</t>
+  </si>
+  <si>
+    <t>OP001078</t>
+  </si>
+  <si>
+    <t>Sunita Gowda</t>
+  </si>
+  <si>
+    <t>9854998086</t>
+  </si>
+  <si>
+    <t>PAT-082904B4</t>
+  </si>
+  <si>
+    <t>OP001079</t>
+  </si>
+  <si>
+    <t>Vikram Sharma</t>
+  </si>
+  <si>
+    <t>9412320161</t>
+  </si>
+  <si>
+    <t>PAT-03471DEF</t>
+  </si>
+  <si>
+    <t>OP001080</t>
+  </si>
+  <si>
+    <t>Aarav Naidu</t>
+  </si>
+  <si>
+    <t>9431507778</t>
+  </si>
+  <si>
+    <t>2026-05-30T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-499CD84B</t>
+  </si>
+  <si>
+    <t>OP001081</t>
+  </si>
+  <si>
+    <t>Ananya Sharma</t>
+  </si>
+  <si>
+    <t>9002554531</t>
+  </si>
+  <si>
+    <t>2026-05-22T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-DE1C909A</t>
+  </si>
+  <si>
+    <t>OP001082</t>
+  </si>
+  <si>
+    <t>Vikram Patel</t>
+  </si>
+  <si>
+    <t>9309277057</t>
+  </si>
+  <si>
+    <t>PAT-2C192CA5</t>
+  </si>
+  <si>
+    <t>OP001083</t>
+  </si>
+  <si>
+    <t>9074837379</t>
+  </si>
+  <si>
+    <t>PAT-844FBE93</t>
+  </si>
+  <si>
+    <t>OP001084</t>
+  </si>
+  <si>
+    <t>Rohan Chowdary</t>
+  </si>
+  <si>
+    <t>9900931340</t>
+  </si>
+  <si>
+    <t>PAT-756DF9D5</t>
+  </si>
+  <si>
+    <t>OP001085</t>
+  </si>
+  <si>
+    <t>Ravi Iyer</t>
+  </si>
+  <si>
+    <t>9325290654</t>
+  </si>
+  <si>
+    <t>PAT-303910CF</t>
+  </si>
+  <si>
+    <t>OP001086</t>
+  </si>
+  <si>
+    <t>Pooja Kumar</t>
+  </si>
+  <si>
+    <t>9395287732</t>
+  </si>
+  <si>
+    <t>PAT-A19A6FEF</t>
+  </si>
+  <si>
+    <t>OP001087</t>
+  </si>
+  <si>
+    <t>Vikram Kumar</t>
+  </si>
+  <si>
+    <t>9298811531</t>
+  </si>
+  <si>
+    <t>PAT-41A52CBC</t>
+  </si>
+  <si>
+    <t>OP001088</t>
+  </si>
+  <si>
+    <t>Diya Rao</t>
+  </si>
+  <si>
+    <t>9699305374</t>
+  </si>
+  <si>
+    <t>2026-05-28T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-18244A7F</t>
+  </si>
+  <si>
+    <t>OP001089</t>
+  </si>
+  <si>
+    <t>9857352412</t>
+  </si>
+  <si>
+    <t>PAT-81CB3987</t>
+  </si>
+  <si>
+    <t>OP001090</t>
+  </si>
+  <si>
+    <t>Sai Reddy</t>
+  </si>
+  <si>
+    <t>9023307534</t>
+  </si>
+  <si>
+    <t>PAT-3F549F8A</t>
+  </si>
+  <si>
+    <t>OP001091</t>
+  </si>
+  <si>
+    <t>9119760749</t>
+  </si>
+  <si>
+    <t>PAT-462077AD</t>
+  </si>
+  <si>
+    <t>OP001092</t>
+  </si>
+  <si>
+    <t>Aarav Reddy</t>
+  </si>
+  <si>
+    <t>9053637175</t>
+  </si>
+  <si>
+    <t>2026-05-12T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-EE12AB2F</t>
+  </si>
+  <si>
+    <t>OP001093</t>
+  </si>
+  <si>
+    <t>Diya Reddy</t>
+  </si>
+  <si>
+    <t>9290494285</t>
+  </si>
+  <si>
+    <t>2026-05-07T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-9F0AE971</t>
+  </si>
+  <si>
+    <t>OP001094</t>
+  </si>
+  <si>
+    <t>Aditya Chowdary</t>
+  </si>
+  <si>
+    <t>9552976193</t>
+  </si>
+  <si>
+    <t>PAT-DF83D28E</t>
+  </si>
+  <si>
+    <t>OP001095</t>
+  </si>
+  <si>
+    <t>9207269729</t>
+  </si>
+  <si>
+    <t>PAT-7A0D47FE</t>
+  </si>
+  <si>
+    <t>OP001096</t>
+  </si>
+  <si>
+    <t>Suresh Chowdary</t>
+  </si>
+  <si>
+    <t>9233607173</t>
+  </si>
+  <si>
+    <t>2026-05-31T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>PAT-070D6DBA</t>
+  </si>
+  <si>
+    <t>OP001097</t>
+  </si>
+  <si>
+    <t>Arjun Menon</t>
+  </si>
+  <si>
+    <t>9951385958</t>
+  </si>
+  <si>
+    <t>2026-05-10T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-2F1BFAB3</t>
+  </si>
+  <si>
+    <t>OP001098</t>
+  </si>
+  <si>
+    <t>Diya Gowda</t>
+  </si>
+  <si>
+    <t>9600300037</t>
+  </si>
+  <si>
+    <t>2026-05-13T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-DF2AC56E</t>
+  </si>
+  <si>
+    <t>OP001099</t>
+  </si>
+  <si>
+    <t>Kavya Iyer</t>
+  </si>
+  <si>
+    <t>9352455416</t>
+  </si>
+  <si>
+    <t>2026-05-28T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-278504B5</t>
+  </si>
+  <si>
+    <t>OP001100</t>
+  </si>
+  <si>
+    <t>Ananya Naidu</t>
+  </si>
+  <si>
+    <t>9823810644</t>
+  </si>
+  <si>
+    <t>2026-05-09T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-9D7EB9B5</t>
+  </si>
+  <si>
+    <t>OP001101</t>
+  </si>
+  <si>
+    <t>Sneha Chowdary</t>
+  </si>
+  <si>
+    <t>9384855165</t>
+  </si>
+  <si>
+    <t>2026-05-19T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-5C57AD13</t>
+  </si>
+  <si>
+    <t>OP001102</t>
+  </si>
+  <si>
+    <t>Kavya Menon</t>
+  </si>
+  <si>
+    <t>9473271699</t>
+  </si>
+  <si>
+    <t>2026-05-29T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-F4C4C74A</t>
+  </si>
+  <si>
+    <t>OP001103</t>
+  </si>
+  <si>
+    <t>Rahul Sharma</t>
+  </si>
+  <si>
+    <t>9486161863</t>
+  </si>
+  <si>
+    <t>2026-05-06T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-A1116C2D</t>
+  </si>
+  <si>
+    <t>OP001104</t>
+  </si>
+  <si>
+    <t>Suresh Sharma</t>
+  </si>
+  <si>
+    <t>9933022665</t>
+  </si>
+  <si>
+    <t>2026-05-30T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-4BB30820</t>
+  </si>
+  <si>
+    <t>OP001105</t>
+  </si>
+  <si>
+    <t>9016902241</t>
+  </si>
+  <si>
+    <t>2026-05-15T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-BA2938F3</t>
+  </si>
+  <si>
+    <t>OP001106</t>
+  </si>
+  <si>
+    <t>9950867422</t>
+  </si>
+  <si>
+    <t>2026-05-08T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-043AFB43</t>
+  </si>
+  <si>
+    <t>OP001107</t>
+  </si>
+  <si>
+    <t>Ramesh Nair</t>
+  </si>
+  <si>
+    <t>9133707137</t>
+  </si>
+  <si>
+    <t>PAT-E077CB90</t>
+  </si>
+  <si>
+    <t>OP001108</t>
+  </si>
+  <si>
+    <t>Priya Gowda</t>
+  </si>
+  <si>
+    <t>9752219518</t>
+  </si>
+  <si>
+    <t>2026-05-25T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-DF35F569</t>
+  </si>
+  <si>
+    <t>OP001109</t>
+  </si>
+  <si>
+    <t>9806146692</t>
+  </si>
+  <si>
+    <t>2026-06-01T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-F94A4E37</t>
+  </si>
+  <si>
+    <t>OP001110</t>
+  </si>
+  <si>
+    <t>Ishita Chowdary</t>
+  </si>
+  <si>
+    <t>9477833367</t>
+  </si>
+  <si>
+    <t>PAT-E220CF76</t>
+  </si>
+  <si>
+    <t>OP001111</t>
+  </si>
+  <si>
+    <t>9285878027</t>
+  </si>
+  <si>
+    <t>2026-05-20T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-5453A20E</t>
+  </si>
+  <si>
+    <t>OP001112</t>
+  </si>
+  <si>
+    <t>Suresh Rao</t>
+  </si>
+  <si>
+    <t>9130955504</t>
+  </si>
+  <si>
+    <t>2026-05-24T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-645BE013</t>
+  </si>
+  <si>
+    <t>OP001113</t>
+  </si>
+  <si>
+    <t>9106573042</t>
+  </si>
+  <si>
+    <t>2026-05-07T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-88BAE112</t>
+  </si>
+  <si>
+    <t>OP001114</t>
+  </si>
+  <si>
+    <t>Krishna Chowdary</t>
+  </si>
+  <si>
+    <t>9182671683</t>
+  </si>
+  <si>
+    <t>2026-05-23T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-18FDAA27</t>
+  </si>
+  <si>
+    <t>OP001115</t>
+  </si>
+  <si>
+    <t>Ramesh Patel</t>
+  </si>
+  <si>
+    <t>9597989958</t>
+  </si>
+  <si>
+    <t>PAT-A7F9BBF4</t>
+  </si>
+  <si>
+    <t>OP001116</t>
+  </si>
+  <si>
+    <t>Ishita Menon</t>
+  </si>
+  <si>
+    <t>9487876377</t>
+  </si>
+  <si>
+    <t>PAT-FFC136BF</t>
+  </si>
+  <si>
+    <t>OP001117</t>
+  </si>
+  <si>
+    <t>Pooja Chowdary</t>
+  </si>
+  <si>
+    <t>9165407993</t>
+  </si>
+  <si>
+    <t>PAT-A8B5DF77</t>
+  </si>
+  <si>
+    <t>OP001118</t>
+  </si>
+  <si>
+    <t>9313885398</t>
+  </si>
+  <si>
+    <t>PAT-98F19C5C</t>
+  </si>
+  <si>
+    <t>OP001119</t>
+  </si>
+  <si>
+    <t>Kavya Kumar</t>
+  </si>
+  <si>
+    <t>9443951290</t>
+  </si>
+  <si>
+    <t>PAT-8FB9A9F4</t>
+  </si>
+  <si>
+    <t>OP002000</t>
+  </si>
+  <si>
+    <t>Scenario A Patient</t>
+  </si>
+  <si>
+    <t>9000000001</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>PAT-9F41BBA2</t>
+  </si>
+  <si>
+    <t>OP002001</t>
+  </si>
+  <si>
+    <t>Scenario B Patient</t>
+  </si>
+  <si>
+    <t>9000000002</t>
+  </si>
+  <si>
+    <t>PAT-006DBDB4</t>
+  </si>
+  <si>
+    <t>OP002002</t>
+  </si>
+  <si>
+    <t>Scenario C Patient</t>
+  </si>
+  <si>
+    <t>9000000003</t>
   </si>
 </sst>
 </file>
@@ -480,10 +2031,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="10" width="25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -514,113 +2074,3941 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="J2">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>72</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15">
+        <v>84</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16">
+        <v>59</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27">
+        <v>67</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28">
+        <v>51</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29">
+        <v>50</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32">
+        <v>55</v>
+      </c>
+      <c r="E32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" t="s">
+        <v>36</v>
+      </c>
+      <c r="J32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33">
+        <v>84</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>36</v>
+      </c>
+      <c r="J33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D34">
+        <v>38</v>
+      </c>
+      <c r="E34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" t="s">
+        <v>155</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35">
+        <v>57</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>159</v>
+      </c>
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36">
+        <v>33</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>163</v>
+      </c>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37">
+        <v>66</v>
+      </c>
+      <c r="E37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>169</v>
+      </c>
+      <c r="B38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38">
+        <v>47</v>
+      </c>
+      <c r="E38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" t="s">
+        <v>172</v>
+      </c>
+      <c r="G38" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>173</v>
+      </c>
+      <c r="B39" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39">
+        <v>58</v>
+      </c>
+      <c r="E39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" t="s">
+        <v>176</v>
+      </c>
+      <c r="G39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40">
+        <v>46</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>180</v>
+      </c>
+      <c r="G40" t="s">
+        <v>35</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" t="s">
+        <v>182</v>
+      </c>
+      <c r="C41" t="s">
+        <v>183</v>
+      </c>
+      <c r="D41">
+        <v>67</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>184</v>
+      </c>
+      <c r="G41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" t="s">
+        <v>36</v>
+      </c>
+      <c r="J41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>185</v>
+      </c>
+      <c r="B42" t="s">
+        <v>186</v>
+      </c>
+      <c r="C42" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42">
+        <v>51</v>
+      </c>
+      <c r="E42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" t="s">
+        <v>188</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>190</v>
+      </c>
+      <c r="B43" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" t="s">
+        <v>192</v>
+      </c>
+      <c r="D43">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" t="s">
+        <v>193</v>
+      </c>
+      <c r="G43" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>195</v>
+      </c>
+      <c r="B44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44">
+        <v>39</v>
+      </c>
+      <c r="E44" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" t="s">
+        <v>198</v>
+      </c>
+      <c r="G44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>200</v>
+      </c>
+      <c r="B45" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" t="s">
+        <v>202</v>
+      </c>
+      <c r="D45">
+        <v>72</v>
+      </c>
+      <c r="E45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" t="s">
+        <v>203</v>
+      </c>
+      <c r="G45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>41</v>
+      </c>
+      <c r="I45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>205</v>
+      </c>
+      <c r="B46" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" t="s">
+        <v>207</v>
+      </c>
+      <c r="D46">
+        <v>38</v>
+      </c>
+      <c r="E46" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" t="s">
+        <v>208</v>
+      </c>
+      <c r="G46" t="s">
+        <v>54</v>
+      </c>
+      <c r="H46" t="s">
+        <v>30</v>
+      </c>
+      <c r="I46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" t="s">
+        <v>211</v>
+      </c>
+      <c r="D47">
+        <v>43</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
+        <v>212</v>
+      </c>
+      <c r="G47" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47" t="s">
+        <v>41</v>
+      </c>
+      <c r="I47" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" t="s">
+        <v>216</v>
+      </c>
+      <c r="D48">
+        <v>66</v>
+      </c>
+      <c r="E48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" t="s">
+        <v>217</v>
+      </c>
+      <c r="G48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" t="s">
+        <v>220</v>
+      </c>
+      <c r="C49" t="s">
+        <v>221</v>
+      </c>
+      <c r="D49">
+        <v>24</v>
+      </c>
+      <c r="E49" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" t="s">
+        <v>222</v>
+      </c>
+      <c r="G49" t="s">
+        <v>104</v>
+      </c>
+      <c r="H49" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>224</v>
+      </c>
+      <c r="B50" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" t="s">
+        <v>226</v>
+      </c>
+      <c r="D50">
+        <v>32</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
+        <v>227</v>
+      </c>
+      <c r="G50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" t="s">
+        <v>230</v>
+      </c>
+      <c r="C51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51">
+        <v>50</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
+        <v>231</v>
+      </c>
+      <c r="G51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H51" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>232</v>
+      </c>
+      <c r="B52" t="s">
+        <v>233</v>
+      </c>
+      <c r="C52" t="s">
+        <v>234</v>
+      </c>
+      <c r="D52">
+        <v>16</v>
+      </c>
+      <c r="E52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" t="s">
+        <v>235</v>
+      </c>
+      <c r="G52" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52" t="s">
+        <v>41</v>
+      </c>
+      <c r="I52" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>236</v>
+      </c>
+      <c r="B53" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" t="s">
+        <v>238</v>
+      </c>
+      <c r="D53">
+        <v>23</v>
+      </c>
+      <c r="E53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" t="s">
+        <v>239</v>
+      </c>
+      <c r="G53" t="s">
+        <v>240</v>
+      </c>
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C54" t="s">
+        <v>243</v>
+      </c>
+      <c r="D54">
+        <v>32</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" t="s">
+        <v>244</v>
+      </c>
+      <c r="G54" t="s">
+        <v>104</v>
+      </c>
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>245</v>
+      </c>
+      <c r="B55" t="s">
+        <v>246</v>
+      </c>
+      <c r="C55" t="s">
+        <v>247</v>
+      </c>
+      <c r="D55">
+        <v>62</v>
+      </c>
+      <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
+        <v>248</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>250</v>
+      </c>
+      <c r="B56" t="s">
+        <v>251</v>
+      </c>
+      <c r="C56" t="s">
+        <v>110</v>
+      </c>
+      <c r="D56">
+        <v>61</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
+        <v>252</v>
+      </c>
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>254</v>
+      </c>
+      <c r="B57" t="s">
+        <v>255</v>
+      </c>
+      <c r="C57" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57">
+        <v>59</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" t="s">
+        <v>257</v>
+      </c>
+      <c r="G57" t="s">
+        <v>54</v>
+      </c>
+      <c r="H57" t="s">
+        <v>30</v>
+      </c>
+      <c r="I57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>259</v>
+      </c>
+      <c r="B58" t="s">
+        <v>260</v>
+      </c>
+      <c r="C58" t="s">
+        <v>261</v>
+      </c>
+      <c r="D58">
+        <v>75</v>
+      </c>
+      <c r="E58" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" t="s">
+        <v>262</v>
+      </c>
+      <c r="G58" t="s">
+        <v>54</v>
+      </c>
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s">
+        <v>36</v>
+      </c>
+      <c r="J58" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>263</v>
+      </c>
+      <c r="B59" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" t="s">
+        <v>265</v>
+      </c>
+      <c r="D59">
+        <v>77</v>
+      </c>
+      <c r="E59" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" t="s">
+        <v>266</v>
+      </c>
+      <c r="G59" t="s">
+        <v>49</v>
+      </c>
+      <c r="H59" t="s">
+        <v>41</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>267</v>
+      </c>
+      <c r="B60" t="s">
+        <v>268</v>
+      </c>
+      <c r="C60" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60">
+        <v>82</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
+        <v>270</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61" t="s">
+        <v>273</v>
+      </c>
+      <c r="C61" t="s">
+        <v>274</v>
+      </c>
+      <c r="D61">
+        <v>33</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
+        <v>275</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>276</v>
+      </c>
+      <c r="B62" t="s">
+        <v>277</v>
+      </c>
+      <c r="C62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D62">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" t="s">
+        <v>279</v>
+      </c>
+      <c r="G62" t="s">
+        <v>35</v>
+      </c>
+      <c r="H62" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>281</v>
+      </c>
+      <c r="B63" t="s">
+        <v>282</v>
+      </c>
+      <c r="C63" t="s">
+        <v>283</v>
+      </c>
+      <c r="D63">
+        <v>14</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
+        <v>284</v>
+      </c>
+      <c r="G63" t="s">
+        <v>29</v>
+      </c>
+      <c r="H63" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>286</v>
+      </c>
+      <c r="B64" t="s">
+        <v>287</v>
+      </c>
+      <c r="C64" t="s">
+        <v>288</v>
+      </c>
+      <c r="D64">
+        <v>32</v>
+      </c>
+      <c r="E64" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" t="s">
+        <v>289</v>
+      </c>
+      <c r="G64" t="s">
+        <v>104</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" t="s">
+        <v>36</v>
+      </c>
+      <c r="J64" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>291</v>
+      </c>
+      <c r="B65" t="s">
+        <v>292</v>
+      </c>
+      <c r="C65" t="s">
+        <v>293</v>
+      </c>
+      <c r="D65">
+        <v>61</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>294</v>
+      </c>
+      <c r="G65" t="s">
+        <v>35</v>
+      </c>
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>296</v>
+      </c>
+      <c r="B66" t="s">
+        <v>297</v>
+      </c>
+      <c r="C66" t="s">
+        <v>298</v>
+      </c>
+      <c r="D66">
+        <v>81</v>
+      </c>
+      <c r="E66" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" t="s">
+        <v>299</v>
+      </c>
+      <c r="G66" t="s">
+        <v>29</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>301</v>
+      </c>
+      <c r="B67" t="s">
+        <v>302</v>
+      </c>
+      <c r="C67" t="s">
+        <v>303</v>
+      </c>
+      <c r="D67">
+        <v>39</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>304</v>
+      </c>
+      <c r="G67" t="s">
+        <v>240</v>
+      </c>
+      <c r="H67" t="s">
+        <v>41</v>
+      </c>
+      <c r="I67" t="s">
+        <v>36</v>
+      </c>
+      <c r="J67" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>306</v>
+      </c>
+      <c r="B68" t="s">
+        <v>307</v>
+      </c>
+      <c r="C68" t="s">
+        <v>308</v>
+      </c>
+      <c r="D68">
+        <v>48</v>
+      </c>
+      <c r="E68" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" t="s">
+        <v>309</v>
+      </c>
+      <c r="G68" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68" t="s">
+        <v>41</v>
+      </c>
+      <c r="I68" t="s">
+        <v>36</v>
+      </c>
+      <c r="J68" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>310</v>
+      </c>
+      <c r="B69" t="s">
+        <v>311</v>
+      </c>
+      <c r="C69" t="s">
+        <v>312</v>
+      </c>
+      <c r="D69">
+        <v>31</v>
+      </c>
+      <c r="E69" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" t="s">
+        <v>313</v>
+      </c>
+      <c r="G69" t="s">
+        <v>104</v>
+      </c>
+      <c r="H69" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>314</v>
+      </c>
+      <c r="B70" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" t="s">
+        <v>316</v>
+      </c>
+      <c r="D70">
+        <v>37</v>
+      </c>
+      <c r="E70" t="s">
+        <v>22</v>
+      </c>
+      <c r="F70" t="s">
+        <v>317</v>
+      </c>
+      <c r="G70" t="s">
+        <v>49</v>
+      </c>
+      <c r="H70" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" t="s">
+        <v>36</v>
+      </c>
+      <c r="J70" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>319</v>
+      </c>
+      <c r="B71" t="s">
+        <v>320</v>
+      </c>
+      <c r="C71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D71">
+        <v>57</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>322</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>323</v>
+      </c>
+      <c r="B72" t="s">
+        <v>324</v>
+      </c>
+      <c r="C72" t="s">
+        <v>325</v>
+      </c>
+      <c r="D72">
+        <v>59</v>
+      </c>
+      <c r="E72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" t="s">
+        <v>326</v>
+      </c>
+      <c r="G72" t="s">
+        <v>49</v>
+      </c>
+      <c r="H72" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>327</v>
+      </c>
+      <c r="B73" t="s">
+        <v>328</v>
+      </c>
+      <c r="C73" t="s">
+        <v>329</v>
+      </c>
+      <c r="D73">
+        <v>40</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>330</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I73" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>331</v>
+      </c>
+      <c r="B74" t="s">
+        <v>332</v>
+      </c>
+      <c r="C74" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74">
+        <v>68</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>333</v>
+      </c>
+      <c r="G74" t="s">
+        <v>104</v>
+      </c>
+      <c r="H74" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>335</v>
+      </c>
+      <c r="B75" t="s">
+        <v>336</v>
+      </c>
+      <c r="C75" t="s">
+        <v>337</v>
+      </c>
+      <c r="D75">
+        <v>67</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
+        <v>338</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>30</v>
+      </c>
+      <c r="I75" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>340</v>
+      </c>
+      <c r="B76" t="s">
+        <v>341</v>
+      </c>
+      <c r="C76" t="s">
+        <v>342</v>
+      </c>
+      <c r="D76">
+        <v>40</v>
+      </c>
+      <c r="E76" t="s">
+        <v>22</v>
+      </c>
+      <c r="F76" t="s">
+        <v>343</v>
+      </c>
+      <c r="G76" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76" t="s">
+        <v>41</v>
+      </c>
+      <c r="I76" t="s">
+        <v>36</v>
+      </c>
+      <c r="J76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>344</v>
+      </c>
+      <c r="B77" t="s">
+        <v>345</v>
+      </c>
+      <c r="C77" t="s">
+        <v>346</v>
+      </c>
+      <c r="D77">
+        <v>72</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>347</v>
+      </c>
+      <c r="G77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H77" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" t="s">
+        <v>24</v>
+      </c>
+      <c r="J77" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>349</v>
+      </c>
+      <c r="B78" t="s">
+        <v>350</v>
+      </c>
+      <c r="C78" t="s">
+        <v>118</v>
+      </c>
+      <c r="D78">
+        <v>19</v>
+      </c>
+      <c r="E78" t="s">
+        <v>22</v>
+      </c>
+      <c r="F78" t="s">
+        <v>351</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>30</v>
+      </c>
+      <c r="I78" t="s">
+        <v>36</v>
+      </c>
+      <c r="J78" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>352</v>
+      </c>
+      <c r="B79" t="s">
+        <v>353</v>
+      </c>
+      <c r="C79" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79">
+        <v>44</v>
+      </c>
+      <c r="E79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" t="s">
+        <v>354</v>
+      </c>
+      <c r="G79" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" t="s">
+        <v>41</v>
+      </c>
+      <c r="I79" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>355</v>
+      </c>
+      <c r="B80" t="s">
+        <v>356</v>
+      </c>
+      <c r="C80" t="s">
+        <v>357</v>
+      </c>
+      <c r="D80">
+        <v>52</v>
+      </c>
+      <c r="E80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F80" t="s">
+        <v>358</v>
+      </c>
+      <c r="G80" t="s">
+        <v>54</v>
+      </c>
+      <c r="H80" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" t="s">
+        <v>36</v>
+      </c>
+      <c r="J80" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>359</v>
+      </c>
+      <c r="B81" t="s">
+        <v>360</v>
+      </c>
+      <c r="C81" t="s">
+        <v>361</v>
+      </c>
+      <c r="D81">
+        <v>73</v>
+      </c>
+      <c r="E81" t="s">
+        <v>22</v>
+      </c>
+      <c r="F81" t="s">
+        <v>362</v>
+      </c>
+      <c r="G81" t="s">
+        <v>35</v>
+      </c>
+      <c r="H81" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" t="s">
+        <v>24</v>
+      </c>
+      <c r="J81" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>363</v>
+      </c>
+      <c r="B82" t="s">
+        <v>364</v>
+      </c>
+      <c r="C82" t="s">
+        <v>365</v>
+      </c>
+      <c r="D82">
+        <v>15</v>
+      </c>
+      <c r="E82" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" t="s">
+        <v>366</v>
+      </c>
+      <c r="G82" t="s">
+        <v>54</v>
+      </c>
+      <c r="H82" t="s">
+        <v>41</v>
+      </c>
+      <c r="I82" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>368</v>
+      </c>
+      <c r="B83" t="s">
+        <v>369</v>
+      </c>
+      <c r="C83" t="s">
+        <v>370</v>
+      </c>
+      <c r="D83">
+        <v>25</v>
+      </c>
+      <c r="E83" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" t="s">
+        <v>371</v>
+      </c>
+      <c r="G83" t="s">
+        <v>54</v>
+      </c>
+      <c r="H83" t="s">
+        <v>30</v>
+      </c>
+      <c r="I83" t="s">
+        <v>24</v>
+      </c>
+      <c r="J83" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>373</v>
+      </c>
+      <c r="B84" t="s">
+        <v>374</v>
+      </c>
+      <c r="C84" t="s">
+        <v>375</v>
+      </c>
+      <c r="D84">
+        <v>27</v>
+      </c>
+      <c r="E84" t="s">
+        <v>22</v>
+      </c>
+      <c r="F84" t="s">
+        <v>376</v>
+      </c>
+      <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" t="s">
+        <v>30</v>
+      </c>
+      <c r="I84" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>377</v>
+      </c>
+      <c r="B85" t="s">
+        <v>378</v>
+      </c>
+      <c r="C85" t="s">
+        <v>274</v>
+      </c>
+      <c r="D85">
+        <v>45</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
+        <v>379</v>
+      </c>
+      <c r="G85" t="s">
+        <v>240</v>
+      </c>
+      <c r="H85" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>380</v>
+      </c>
+      <c r="B86" t="s">
+        <v>381</v>
+      </c>
+      <c r="C86" t="s">
+        <v>382</v>
+      </c>
+      <c r="D86">
+        <v>46</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
+        <v>383</v>
+      </c>
+      <c r="G86" t="s">
+        <v>49</v>
+      </c>
+      <c r="H86" t="s">
+        <v>30</v>
+      </c>
+      <c r="I86" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>384</v>
+      </c>
+      <c r="B87" t="s">
+        <v>385</v>
+      </c>
+      <c r="C87" t="s">
+        <v>386</v>
+      </c>
+      <c r="D87">
+        <v>52</v>
+      </c>
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" t="s">
+        <v>387</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>30</v>
+      </c>
+      <c r="I87" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>388</v>
+      </c>
+      <c r="B88" t="s">
+        <v>389</v>
+      </c>
+      <c r="C88" t="s">
+        <v>390</v>
+      </c>
+      <c r="D88">
+        <v>31</v>
+      </c>
+      <c r="E88" t="s">
+        <v>22</v>
+      </c>
+      <c r="F88" t="s">
+        <v>391</v>
+      </c>
+      <c r="G88" t="s">
+        <v>54</v>
+      </c>
+      <c r="H88" t="s">
+        <v>41</v>
+      </c>
+      <c r="I88" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>392</v>
+      </c>
+      <c r="B89" t="s">
+        <v>393</v>
+      </c>
+      <c r="C89" t="s">
+        <v>394</v>
+      </c>
+      <c r="D89">
+        <v>60</v>
+      </c>
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>395</v>
+      </c>
+      <c r="G89" t="s">
+        <v>49</v>
+      </c>
+      <c r="H89" t="s">
+        <v>41</v>
+      </c>
+      <c r="I89" t="s">
+        <v>24</v>
+      </c>
+      <c r="J89" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>396</v>
+      </c>
+      <c r="B90" t="s">
+        <v>397</v>
+      </c>
+      <c r="C90" t="s">
+        <v>398</v>
+      </c>
+      <c r="D90">
+        <v>53</v>
+      </c>
+      <c r="E90" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" t="s">
+        <v>399</v>
+      </c>
+      <c r="G90" t="s">
+        <v>49</v>
+      </c>
+      <c r="H90" t="s">
+        <v>41</v>
+      </c>
+      <c r="I90" t="s">
+        <v>36</v>
+      </c>
+      <c r="J90" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>401</v>
+      </c>
+      <c r="B91" t="s">
+        <v>402</v>
+      </c>
+      <c r="C91" t="s">
+        <v>386</v>
+      </c>
+      <c r="D91">
+        <v>67</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>403</v>
+      </c>
+      <c r="G91" t="s">
+        <v>91</v>
+      </c>
+      <c r="H91" t="s">
+        <v>41</v>
+      </c>
+      <c r="I91" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>404</v>
+      </c>
+      <c r="B92" t="s">
+        <v>405</v>
+      </c>
+      <c r="C92" t="s">
+        <v>406</v>
+      </c>
+      <c r="D92">
+        <v>33</v>
+      </c>
+      <c r="E92" t="s">
+        <v>22</v>
+      </c>
+      <c r="F92" t="s">
+        <v>407</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
+        <v>30</v>
+      </c>
+      <c r="I92" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>408</v>
+      </c>
+      <c r="B93" t="s">
+        <v>409</v>
+      </c>
+      <c r="C93" t="s">
+        <v>243</v>
+      </c>
+      <c r="D93">
+        <v>47</v>
+      </c>
+      <c r="E93" t="s">
+        <v>22</v>
+      </c>
+      <c r="F93" t="s">
+        <v>410</v>
+      </c>
+      <c r="G93" t="s">
+        <v>91</v>
+      </c>
+      <c r="H93" t="s">
+        <v>30</v>
+      </c>
+      <c r="I93" t="s">
+        <v>36</v>
+      </c>
+      <c r="J93" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>411</v>
+      </c>
+      <c r="B94" t="s">
+        <v>412</v>
+      </c>
+      <c r="C94" t="s">
+        <v>413</v>
+      </c>
+      <c r="D94">
+        <v>79</v>
+      </c>
+      <c r="E94" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" t="s">
+        <v>414</v>
+      </c>
+      <c r="G94" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" t="s">
+        <v>36</v>
+      </c>
+      <c r="J94" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>416</v>
+      </c>
+      <c r="B95" t="s">
+        <v>417</v>
+      </c>
+      <c r="C95" t="s">
+        <v>418</v>
+      </c>
+      <c r="D95">
+        <v>35</v>
+      </c>
+      <c r="E95" t="s">
+        <v>22</v>
+      </c>
+      <c r="F95" t="s">
+        <v>419</v>
+      </c>
+      <c r="G95" t="s">
+        <v>240</v>
+      </c>
+      <c r="H95" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" t="s">
+        <v>36</v>
+      </c>
+      <c r="J95" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>421</v>
+      </c>
+      <c r="B96" t="s">
+        <v>422</v>
+      </c>
+      <c r="C96" t="s">
+        <v>423</v>
+      </c>
+      <c r="D96">
+        <v>66</v>
+      </c>
+      <c r="E96" t="s">
+        <v>22</v>
+      </c>
+      <c r="F96" t="s">
+        <v>424</v>
+      </c>
+      <c r="G96" t="s">
+        <v>54</v>
+      </c>
+      <c r="H96" t="s">
+        <v>30</v>
+      </c>
+      <c r="I96" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>425</v>
+      </c>
+      <c r="B97" t="s">
+        <v>426</v>
+      </c>
+      <c r="C97" t="s">
+        <v>390</v>
+      </c>
+      <c r="D97">
+        <v>23</v>
+      </c>
+      <c r="E97" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" t="s">
+        <v>427</v>
+      </c>
+      <c r="G97" t="s">
+        <v>240</v>
+      </c>
+      <c r="H97" t="s">
+        <v>30</v>
+      </c>
+      <c r="I97" t="s">
+        <v>36</v>
+      </c>
+      <c r="J97" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>428</v>
+      </c>
+      <c r="B98" t="s">
+        <v>429</v>
+      </c>
+      <c r="C98" t="s">
+        <v>430</v>
+      </c>
+      <c r="D98">
+        <v>77</v>
+      </c>
+      <c r="E98" t="s">
+        <v>22</v>
+      </c>
+      <c r="F98" t="s">
+        <v>431</v>
+      </c>
+      <c r="G98" t="s">
+        <v>54</v>
+      </c>
+      <c r="H98" t="s">
+        <v>41</v>
+      </c>
+      <c r="I98" t="s">
+        <v>24</v>
+      </c>
+      <c r="J98" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>433</v>
+      </c>
+      <c r="B99" t="s">
+        <v>434</v>
+      </c>
+      <c r="C99" t="s">
+        <v>435</v>
+      </c>
+      <c r="D99">
+        <v>67</v>
+      </c>
+      <c r="E99" t="s">
+        <v>22</v>
+      </c>
+      <c r="F99" t="s">
+        <v>436</v>
+      </c>
+      <c r="G99" t="s">
+        <v>54</v>
+      </c>
+      <c r="H99" t="s">
+        <v>41</v>
+      </c>
+      <c r="I99" t="s">
+        <v>36</v>
+      </c>
+      <c r="J99" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>438</v>
+      </c>
+      <c r="B100" t="s">
+        <v>439</v>
+      </c>
+      <c r="C100" t="s">
+        <v>440</v>
+      </c>
+      <c r="D100">
+        <v>44</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" t="s">
+        <v>441</v>
+      </c>
+      <c r="G100" t="s">
+        <v>29</v>
+      </c>
+      <c r="H100" t="s">
+        <v>41</v>
+      </c>
+      <c r="I100" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>443</v>
+      </c>
+      <c r="B101" t="s">
+        <v>444</v>
+      </c>
+      <c r="C101" t="s">
+        <v>445</v>
+      </c>
+      <c r="D101">
+        <v>23</v>
+      </c>
+      <c r="E101" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" t="s">
+        <v>446</v>
+      </c>
+      <c r="G101" t="s">
+        <v>54</v>
+      </c>
+      <c r="H101" t="s">
+        <v>41</v>
+      </c>
+      <c r="I101" t="s">
+        <v>36</v>
+      </c>
+      <c r="J101" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>448</v>
+      </c>
+      <c r="B102" t="s">
+        <v>449</v>
+      </c>
+      <c r="C102" t="s">
+        <v>450</v>
+      </c>
+      <c r="D102">
+        <v>67</v>
+      </c>
+      <c r="E102" t="s">
+        <v>22</v>
+      </c>
+      <c r="F102" t="s">
+        <v>451</v>
+      </c>
+      <c r="G102" t="s">
+        <v>104</v>
+      </c>
+      <c r="H102" t="s">
+        <v>30</v>
+      </c>
+      <c r="I102" t="s">
+        <v>24</v>
+      </c>
+      <c r="J102" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>453</v>
+      </c>
+      <c r="B103" t="s">
+        <v>454</v>
+      </c>
+      <c r="C103" t="s">
+        <v>455</v>
+      </c>
+      <c r="D103">
+        <v>44</v>
+      </c>
+      <c r="E103" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" t="s">
+        <v>456</v>
+      </c>
+      <c r="G103" t="s">
+        <v>35</v>
+      </c>
+      <c r="H103" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>458</v>
+      </c>
+      <c r="B104" t="s">
+        <v>459</v>
+      </c>
+      <c r="C104" t="s">
+        <v>460</v>
+      </c>
+      <c r="D104">
+        <v>60</v>
+      </c>
+      <c r="E104" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" t="s">
+        <v>461</v>
+      </c>
+      <c r="G104" t="s">
+        <v>240</v>
+      </c>
+      <c r="H104" t="s">
+        <v>41</v>
+      </c>
+      <c r="I104" t="s">
+        <v>36</v>
+      </c>
+      <c r="J104" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>463</v>
+      </c>
+      <c r="B105" t="s">
+        <v>464</v>
+      </c>
+      <c r="C105" t="s">
+        <v>465</v>
+      </c>
+      <c r="D105">
+        <v>73</v>
+      </c>
+      <c r="E105" t="s">
+        <v>22</v>
+      </c>
+      <c r="F105" t="s">
+        <v>466</v>
+      </c>
+      <c r="G105" t="s">
+        <v>49</v>
+      </c>
+      <c r="H105" t="s">
+        <v>41</v>
+      </c>
+      <c r="I105" t="s">
+        <v>36</v>
+      </c>
+      <c r="J105" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>468</v>
+      </c>
+      <c r="B106" t="s">
+        <v>469</v>
+      </c>
+      <c r="C106" t="s">
+        <v>470</v>
+      </c>
+      <c r="D106">
+        <v>48</v>
+      </c>
+      <c r="E106" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" t="s">
+        <v>471</v>
+      </c>
+      <c r="G106" t="s">
+        <v>54</v>
+      </c>
+      <c r="H106" t="s">
+        <v>30</v>
+      </c>
+      <c r="I106" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>473</v>
+      </c>
+      <c r="B107" t="s">
+        <v>474</v>
+      </c>
+      <c r="C107" t="s">
+        <v>465</v>
+      </c>
+      <c r="D107">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" t="s">
+        <v>475</v>
+      </c>
+      <c r="G107" t="s">
+        <v>91</v>
+      </c>
+      <c r="H107" t="s">
+        <v>30</v>
+      </c>
+      <c r="I107" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>477</v>
+      </c>
+      <c r="B108" t="s">
+        <v>478</v>
+      </c>
+      <c r="C108" t="s">
+        <v>321</v>
+      </c>
+      <c r="D108">
+        <v>48</v>
+      </c>
+      <c r="E108" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" t="s">
+        <v>479</v>
+      </c>
+      <c r="G108" t="s">
+        <v>49</v>
+      </c>
+      <c r="H108" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" t="s">
+        <v>36</v>
+      </c>
+      <c r="J108" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>481</v>
+      </c>
+      <c r="B109" t="s">
+        <v>482</v>
+      </c>
+      <c r="C109" t="s">
+        <v>483</v>
+      </c>
+      <c r="D109">
+        <v>10</v>
+      </c>
+      <c r="E109" t="s">
+        <v>22</v>
+      </c>
+      <c r="F109" t="s">
+        <v>484</v>
+      </c>
+      <c r="G109" t="s">
+        <v>35</v>
+      </c>
+      <c r="H109" t="s">
+        <v>16</v>
+      </c>
+      <c r="I109" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>485</v>
+      </c>
+      <c r="B110" t="s">
+        <v>486</v>
+      </c>
+      <c r="C110" t="s">
+        <v>487</v>
+      </c>
+      <c r="D110">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" t="s">
+        <v>488</v>
+      </c>
+      <c r="G110" t="s">
+        <v>91</v>
+      </c>
+      <c r="H110" t="s">
+        <v>30</v>
+      </c>
+      <c r="I110" t="s">
+        <v>24</v>
+      </c>
+      <c r="J110" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>490</v>
+      </c>
+      <c r="B111" t="s">
+        <v>491</v>
+      </c>
+      <c r="C111" t="s">
+        <v>243</v>
+      </c>
+      <c r="D111">
+        <v>67</v>
+      </c>
+      <c r="E111" t="s">
+        <v>22</v>
+      </c>
+      <c r="F111" t="s">
+        <v>492</v>
+      </c>
+      <c r="G111" t="s">
+        <v>29</v>
+      </c>
+      <c r="H111" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" t="s">
+        <v>24</v>
+      </c>
+      <c r="J111" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>494</v>
+      </c>
+      <c r="B112" t="s">
+        <v>495</v>
+      </c>
+      <c r="C112" t="s">
+        <v>496</v>
+      </c>
+      <c r="D112">
+        <v>22</v>
+      </c>
+      <c r="E112" t="s">
+        <v>22</v>
+      </c>
+      <c r="F112" t="s">
+        <v>497</v>
+      </c>
+      <c r="G112" t="s">
+        <v>54</v>
+      </c>
+      <c r="H112" t="s">
+        <v>41</v>
+      </c>
+      <c r="I112" t="s">
+        <v>24</v>
+      </c>
+      <c r="J112" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>498</v>
+      </c>
+      <c r="B113" t="s">
+        <v>499</v>
+      </c>
+      <c r="C113" t="s">
+        <v>435</v>
+      </c>
+      <c r="D113">
+        <v>62</v>
+      </c>
+      <c r="E113" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" t="s">
         <v>500</v>
       </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G113" t="s">
+        <v>49</v>
+      </c>
+      <c r="H113" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" t="s">
+        <v>17</v>
+      </c>
+      <c r="J113" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>502</v>
+      </c>
+      <c r="B114" t="s">
+        <v>503</v>
+      </c>
+      <c r="C114" t="s">
+        <v>504</v>
+      </c>
+      <c r="D114">
+        <v>83</v>
+      </c>
+      <c r="E114" t="s">
+        <v>22</v>
+      </c>
+      <c r="F114" t="s">
+        <v>505</v>
+      </c>
+      <c r="G114" t="s">
+        <v>49</v>
+      </c>
+      <c r="H114" t="s">
+        <v>30</v>
+      </c>
+      <c r="I114" t="s">
+        <v>36</v>
+      </c>
+      <c r="J114" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>507</v>
+      </c>
+      <c r="B115" t="s">
+        <v>508</v>
+      </c>
+      <c r="C115" t="s">
+        <v>52</v>
+      </c>
+      <c r="D115">
+        <v>17</v>
+      </c>
+      <c r="E115" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="F115" t="s">
+        <v>509</v>
+      </c>
+      <c r="G115" t="s">
+        <v>49</v>
+      </c>
+      <c r="H115" t="s">
+        <v>41</v>
+      </c>
+      <c r="I115" t="s">
+        <v>24</v>
+      </c>
+      <c r="J115" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>511</v>
+      </c>
+      <c r="B116" t="s">
+        <v>512</v>
+      </c>
+      <c r="C116" t="s">
+        <v>513</v>
+      </c>
+      <c r="D116">
+        <v>41</v>
+      </c>
+      <c r="E116" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" t="s">
+        <v>514</v>
+      </c>
+      <c r="G116" t="s">
+        <v>104</v>
+      </c>
+      <c r="H116" t="s">
+        <v>41</v>
+      </c>
+      <c r="I116" t="s">
+        <v>24</v>
+      </c>
+      <c r="J116" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>516</v>
+      </c>
+      <c r="B117" t="s">
+        <v>517</v>
+      </c>
+      <c r="C117" t="s">
+        <v>518</v>
+      </c>
+      <c r="D117">
+        <v>69</v>
+      </c>
+      <c r="E117" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" t="s">
+        <v>519</v>
+      </c>
+      <c r="G117" t="s">
+        <v>240</v>
+      </c>
+      <c r="H117" t="s">
+        <v>16</v>
+      </c>
+      <c r="I117" t="s">
+        <v>36</v>
+      </c>
+      <c r="J117" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>520</v>
+      </c>
+      <c r="B118" t="s">
+        <v>521</v>
+      </c>
+      <c r="C118" t="s">
+        <v>522</v>
+      </c>
+      <c r="D118">
+        <v>84</v>
+      </c>
+      <c r="E118" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" t="s">
+        <v>523</v>
+      </c>
+      <c r="G118" t="s">
+        <v>104</v>
+      </c>
+      <c r="H118" t="s">
+        <v>41</v>
+      </c>
+      <c r="I118" t="s">
+        <v>36</v>
+      </c>
+      <c r="J118" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>524</v>
+      </c>
+      <c r="B119" t="s">
+        <v>525</v>
+      </c>
+      <c r="C119" t="s">
+        <v>526</v>
+      </c>
+      <c r="D119">
+        <v>62</v>
+      </c>
+      <c r="E119" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" t="s">
+        <v>527</v>
+      </c>
+      <c r="G119" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H119" t="s">
+        <v>30</v>
+      </c>
+      <c r="I119" t="s">
+        <v>24</v>
+      </c>
+      <c r="J119" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>528</v>
+      </c>
+      <c r="B120" t="s">
+        <v>529</v>
+      </c>
+      <c r="C120" t="s">
+        <v>154</v>
+      </c>
+      <c r="D120">
+        <v>18</v>
+      </c>
+      <c r="E120" t="s">
+        <v>22</v>
+      </c>
+      <c r="F120" t="s">
+        <v>530</v>
+      </c>
+      <c r="G120" t="s">
+        <v>91</v>
+      </c>
+      <c r="H120" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I120" t="s">
+        <v>36</v>
+      </c>
+      <c r="J120" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>531</v>
+      </c>
+      <c r="B121" t="s">
+        <v>532</v>
+      </c>
+      <c r="C121" t="s">
+        <v>533</v>
+      </c>
+      <c r="D121">
+        <v>63</v>
+      </c>
+      <c r="E121" t="s">
+        <v>22</v>
+      </c>
+      <c r="F121" t="s">
+        <v>534</v>
+      </c>
+      <c r="G121" t="s">
+        <v>29</v>
+      </c>
+      <c r="H121" t="s">
+        <v>16</v>
+      </c>
+      <c r="I121" t="s">
+        <v>36</v>
+      </c>
+      <c r="J121" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>535</v>
+      </c>
+      <c r="B122" t="s">
+        <v>536</v>
+      </c>
+      <c r="C122" t="s">
+        <v>537</v>
+      </c>
+      <c r="D122">
+        <v>45</v>
+      </c>
+      <c r="E122" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" t="s">
+        <v>538</v>
+      </c>
+      <c r="G122" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" t="s">
+        <v>41</v>
+      </c>
+      <c r="I122" t="s">
+        <v>36</v>
+      </c>
+      <c r="J122" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>540</v>
+      </c>
+      <c r="B123" t="s">
+        <v>541</v>
+      </c>
+      <c r="C123" t="s">
+        <v>542</v>
+      </c>
+      <c r="D123">
+        <v>60</v>
+      </c>
+      <c r="E123" t="s">
+        <v>22</v>
+      </c>
+      <c r="F123" t="s">
+        <v>543</v>
+      </c>
+      <c r="G123" t="s">
+        <v>35</v>
+      </c>
+      <c r="H123" t="s">
+        <v>41</v>
+      </c>
+      <c r="I123" t="s">
+        <v>24</v>
+      </c>
+      <c r="J123" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>544</v>
+      </c>
+      <c r="B124" t="s">
+        <v>545</v>
+      </c>
+      <c r="C124" t="s">
+        <v>546</v>
+      </c>
+      <c r="D124">
+        <v>55</v>
+      </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" t="s">
+        <v>547</v>
+      </c>
+      <c r="G124" t="s">
+        <v>91</v>
+      </c>
+      <c r="H124" t="s">
+        <v>41</v>
+      </c>
+      <c r="I124" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3">
-        <v>500</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4">
-        <v>500</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
+      <c r="J124" t="s">
+        <v>539</v>
       </c>
     </row>
   </sheetData>
